--- a/results/Summary_FRAMES_Results.xlsx
+++ b/results/Summary_FRAMES_Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d34c2155fed882aa/Chatbot/Evaluation/09_march/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UPB\master-thesis\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{394D90D7-9DCA-4C90-9549-4D0288BE9204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ACA7869-154B-4345-A468-A9FBEF0D448D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6305CDB0-4070-4D91-A51E-E9D9D42F74FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenAI GPT-4.1 FRAMES" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
   <si>
     <t>Evaluation results (FRAMES core retrieval comparison)</t>
   </si>
@@ -50,6 +50,18 @@
   </si>
   <si>
     <t>Configuration: query expansion disabled, reranking disabled, and multi-hop retrieval disabled</t>
+  </si>
+  <si>
+    <t>Evaluation results (FRAMES multi-hop retrieval comparison with OpenAI GPT-4.1)</t>
+  </si>
+  <si>
+    <t>BM25 baseline with multi-hop retrieval</t>
+  </si>
+  <si>
+    <t>Hybrid pipeline with multi-hop retrieval</t>
+  </si>
+  <si>
+    <t>Configuration: Query expansion disabled, reranking disabled, and multi-hop retrieval enabled</t>
   </si>
 </sst>
 </file>
@@ -59,7 +71,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +102,26 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -132,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -147,6 +179,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -583,10 +627,76 @@
         <v>9</v>
       </c>
     </row>
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0.19040000000000001</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.59930000000000005</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.35039999999999999</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0.19889999999999999</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.62070000000000003</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0.40479999999999999</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="J1:N1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
